--- a/templates/opportunities_import.xlsx
+++ b/templates/opportunities_import.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opportunities" sheetId="1" r:id="R6f4964ac375d4f13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R542802ab761b434c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opportunities" sheetId="1" r:id="Rfd73a97b28174615"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="Rd496ed548a1348fc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -360,7 +360,7 @@
         <x:color rgb="FFA12B20"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE5E0"/>
         </x:patternFill>
       </x:fill>
@@ -371,7 +371,7 @@
         <x:color rgb="FFA12B20"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE5E0"/>
         </x:patternFill>
       </x:fill>
@@ -381,9 +381,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OpportunityEntries" displayName="OpportunityEntries" ref="A7:O107" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:O107"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OpportunityEntries" displayName="OpportunityEntries" ref="A7:N107" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:N107"/>
+  <x:tableColumns count="14">
     <x:tableColumn id="1" name="Project Name"/>
     <x:tableColumn id="2" name="Region"/>
     <x:tableColumn id="3" name="Closing Date&#10;(dd/mm/yyyy)"/>
@@ -395,10 +395,9 @@
     <x:tableColumn id="9" name="Estimated value (AUD)"/>
     <x:tableColumn id="10" name="Distance (km)"/>
     <x:tableColumn id="11" name="Distance Origin"/>
-    <x:tableColumn id="12" name="Contact person"/>
-    <x:tableColumn id="13" name="Email"/>
+    <x:tableColumn id="12" name="Link"/>
+    <x:tableColumn id="13" name="Notes"/>
     <x:tableColumn id="14" name="Added Date&#10;(dd/mm/yyyy)"/>
-    <x:tableColumn id="15" name="Notes"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -613,8 +612,8 @@
     <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="49" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="28" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="34" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="49" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="49" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="20" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="49" hidden="0" customWidth="1"/>
   </x:cols>
@@ -634,7 +633,7 @@
       <x:c r="L1" s="2"/>
       <x:c r="M1" s="2"/>
       <x:c r="N1" s="2"/>
-      <x:c r="O1" s="2"/>
+      <x:c r="O1"/>
     </x:row>
     <x:row r="2" ht="29" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -653,7 +652,7 @@
       <x:c r="L2" s="2"/>
       <x:c r="M2" s="2"/>
       <x:c r="N2" s="2"/>
-      <x:c r="O2" s="2"/>
+      <x:c r="O2"/>
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="5" t="str">
@@ -672,7 +671,7 @@
       <x:c r="L3" s="6"/>
       <x:c r="M3" s="6"/>
       <x:c r="N3" s="6"/>
-      <x:c r="O3" s="6"/>
+      <x:c r="O3"/>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
       <x:c r="A4" s="4" t="str">
@@ -691,7 +690,7 @@
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
       <x:c r="N4" s="4"/>
-      <x:c r="O4" s="4"/>
+      <x:c r="O4"/>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
       <x:c r="A5" s="4" t="str">
@@ -710,7 +709,7 @@
       <x:c r="L5" s="4"/>
       <x:c r="M5" s="4"/>
       <x:c r="N5" s="4"/>
-      <x:c r="O5" s="4"/>
+      <x:c r="O5"/>
     </x:row>
     <x:row r="6" ht="10" customHeight="1">
       <x:c r="A6" s="2"/>
@@ -727,7 +726,7 @@
       <x:c r="L6" s="2"/>
       <x:c r="M6" s="2"/>
       <x:c r="N6" s="2"/>
-      <x:c r="O6" s="2"/>
+      <x:c r="O6"/>
     </x:row>
     <x:row r="7" ht="46" customHeight="1">
       <x:c r="A7" s="25" t="str">
@@ -765,18 +764,16 @@
         <x:v>Distance Origin</x:v>
       </x:c>
       <x:c r="L7" s="26" t="str">
-        <x:v>Contact person</x:v>
-      </x:c>
-      <x:c r="M7" s="26" t="str">
-        <x:v>Email</x:v>
+        <x:v>Link</x:v>
+      </x:c>
+      <x:c r="M7" s="27" t="str">
+        <x:v>Notes</x:v>
       </x:c>
       <x:c r="N7" s="26" t="str">
         <x:v>Added Date
 (dd/mm/yyyy)</x:v>
       </x:c>
-      <x:c r="O7" s="27" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
+      <x:c r="O7"/>
     </x:row>
     <x:row r="8" ht="36" customHeight="1">
       <x:c r="A8" s="28"/>
@@ -793,7 +790,7 @@
       <x:c r="L8" s="29"/>
       <x:c r="M8" s="29"/>
       <x:c r="N8" s="37"/>
-      <x:c r="O8" s="29"/>
+      <x:c r="O8"/>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
       <x:c r="A9" s="30"/>
@@ -810,7 +807,7 @@
       <x:c r="L9" s="31"/>
       <x:c r="M9" s="31"/>
       <x:c r="N9" s="38"/>
-      <x:c r="O9" s="31"/>
+      <x:c r="O9"/>
     </x:row>
     <x:row r="10" ht="36" customHeight="1">
       <x:c r="A10" s="30"/>
@@ -827,7 +824,7 @@
       <x:c r="L10" s="31"/>
       <x:c r="M10" s="31"/>
       <x:c r="N10" s="38"/>
-      <x:c r="O10" s="31"/>
+      <x:c r="O10"/>
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
       <x:c r="A11" s="30"/>
@@ -844,7 +841,7 @@
       <x:c r="L11" s="31"/>
       <x:c r="M11" s="31"/>
       <x:c r="N11" s="38"/>
-      <x:c r="O11" s="31"/>
+      <x:c r="O11"/>
     </x:row>
     <x:row r="12" ht="36" customHeight="1">
       <x:c r="A12" s="30"/>
@@ -861,7 +858,7 @@
       <x:c r="L12" s="31"/>
       <x:c r="M12" s="31"/>
       <x:c r="N12" s="38"/>
-      <x:c r="O12" s="31"/>
+      <x:c r="O12"/>
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
       <x:c r="A13" s="30"/>
@@ -878,7 +875,7 @@
       <x:c r="L13" s="31"/>
       <x:c r="M13" s="31"/>
       <x:c r="N13" s="38"/>
-      <x:c r="O13" s="31"/>
+      <x:c r="O13"/>
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
       <x:c r="A14" s="30"/>
@@ -895,7 +892,7 @@
       <x:c r="L14" s="31"/>
       <x:c r="M14" s="31"/>
       <x:c r="N14" s="38"/>
-      <x:c r="O14" s="31"/>
+      <x:c r="O14"/>
     </x:row>
     <x:row r="15" ht="36" customHeight="1">
       <x:c r="A15" s="30"/>
@@ -912,7 +909,7 @@
       <x:c r="L15" s="31"/>
       <x:c r="M15" s="31"/>
       <x:c r="N15" s="38"/>
-      <x:c r="O15" s="31"/>
+      <x:c r="O15"/>
     </x:row>
     <x:row r="16" ht="36" customHeight="1">
       <x:c r="A16" s="30"/>
@@ -929,7 +926,7 @@
       <x:c r="L16" s="31"/>
       <x:c r="M16" s="31"/>
       <x:c r="N16" s="38"/>
-      <x:c r="O16" s="31"/>
+      <x:c r="O16"/>
     </x:row>
     <x:row r="17" ht="36" customHeight="1">
       <x:c r="A17" s="30"/>
@@ -946,7 +943,7 @@
       <x:c r="L17" s="31"/>
       <x:c r="M17" s="31"/>
       <x:c r="N17" s="38"/>
-      <x:c r="O17" s="31"/>
+      <x:c r="O17"/>
     </x:row>
     <x:row r="18" ht="36" customHeight="1">
       <x:c r="A18" s="30"/>
@@ -963,7 +960,7 @@
       <x:c r="L18" s="31"/>
       <x:c r="M18" s="31"/>
       <x:c r="N18" s="38"/>
-      <x:c r="O18" s="31"/>
+      <x:c r="O18"/>
     </x:row>
     <x:row r="19" ht="36" customHeight="1">
       <x:c r="A19" s="30"/>
@@ -980,7 +977,7 @@
       <x:c r="L19" s="31"/>
       <x:c r="M19" s="31"/>
       <x:c r="N19" s="38"/>
-      <x:c r="O19" s="31"/>
+      <x:c r="O19"/>
     </x:row>
     <x:row r="20" ht="36" customHeight="1">
       <x:c r="A20" s="30"/>
@@ -997,7 +994,7 @@
       <x:c r="L20" s="31"/>
       <x:c r="M20" s="31"/>
       <x:c r="N20" s="38"/>
-      <x:c r="O20" s="31"/>
+      <x:c r="O20"/>
     </x:row>
     <x:row r="21" ht="36" customHeight="1">
       <x:c r="A21" s="30"/>
@@ -1014,7 +1011,7 @@
       <x:c r="L21" s="31"/>
       <x:c r="M21" s="31"/>
       <x:c r="N21" s="38"/>
-      <x:c r="O21" s="31"/>
+      <x:c r="O21"/>
     </x:row>
     <x:row r="22" ht="36" customHeight="1">
       <x:c r="A22" s="30"/>
@@ -1031,7 +1028,7 @@
       <x:c r="L22" s="31"/>
       <x:c r="M22" s="31"/>
       <x:c r="N22" s="38"/>
-      <x:c r="O22" s="31"/>
+      <x:c r="O22"/>
     </x:row>
     <x:row r="23" ht="36" customHeight="1">
       <x:c r="A23" s="30"/>
@@ -1048,7 +1045,7 @@
       <x:c r="L23" s="31"/>
       <x:c r="M23" s="31"/>
       <x:c r="N23" s="38"/>
-      <x:c r="O23" s="31"/>
+      <x:c r="O23"/>
     </x:row>
     <x:row r="24" ht="36" customHeight="1">
       <x:c r="A24" s="30"/>
@@ -1065,7 +1062,7 @@
       <x:c r="L24" s="31"/>
       <x:c r="M24" s="31"/>
       <x:c r="N24" s="38"/>
-      <x:c r="O24" s="31"/>
+      <x:c r="O24"/>
     </x:row>
     <x:row r="25" ht="36" customHeight="1">
       <x:c r="A25" s="30"/>
@@ -1082,7 +1079,7 @@
       <x:c r="L25" s="31"/>
       <x:c r="M25" s="31"/>
       <x:c r="N25" s="38"/>
-      <x:c r="O25" s="31"/>
+      <x:c r="O25"/>
     </x:row>
     <x:row r="26" ht="36" customHeight="1">
       <x:c r="A26" s="30"/>
@@ -1099,7 +1096,7 @@
       <x:c r="L26" s="31"/>
       <x:c r="M26" s="31"/>
       <x:c r="N26" s="38"/>
-      <x:c r="O26" s="31"/>
+      <x:c r="O26"/>
     </x:row>
     <x:row r="27" ht="36" customHeight="1">
       <x:c r="A27" s="30"/>
@@ -1116,7 +1113,7 @@
       <x:c r="L27" s="31"/>
       <x:c r="M27" s="31"/>
       <x:c r="N27" s="38"/>
-      <x:c r="O27" s="31"/>
+      <x:c r="O27"/>
     </x:row>
     <x:row r="28" ht="36" customHeight="1">
       <x:c r="A28" s="30"/>
@@ -1133,7 +1130,7 @@
       <x:c r="L28" s="31"/>
       <x:c r="M28" s="31"/>
       <x:c r="N28" s="38"/>
-      <x:c r="O28" s="31"/>
+      <x:c r="O28"/>
     </x:row>
     <x:row r="29" ht="36" customHeight="1">
       <x:c r="A29" s="30"/>
@@ -1150,7 +1147,7 @@
       <x:c r="L29" s="31"/>
       <x:c r="M29" s="31"/>
       <x:c r="N29" s="38"/>
-      <x:c r="O29" s="31"/>
+      <x:c r="O29"/>
     </x:row>
     <x:row r="30" ht="36" customHeight="1">
       <x:c r="A30" s="30"/>
@@ -1167,7 +1164,7 @@
       <x:c r="L30" s="31"/>
       <x:c r="M30" s="31"/>
       <x:c r="N30" s="38"/>
-      <x:c r="O30" s="31"/>
+      <x:c r="O30"/>
     </x:row>
     <x:row r="31" ht="36" customHeight="1">
       <x:c r="A31" s="30"/>
@@ -1184,7 +1181,7 @@
       <x:c r="L31" s="31"/>
       <x:c r="M31" s="31"/>
       <x:c r="N31" s="38"/>
-      <x:c r="O31" s="31"/>
+      <x:c r="O31"/>
     </x:row>
     <x:row r="32" ht="36" customHeight="1">
       <x:c r="A32" s="30"/>
@@ -1201,7 +1198,7 @@
       <x:c r="L32" s="31"/>
       <x:c r="M32" s="31"/>
       <x:c r="N32" s="38"/>
-      <x:c r="O32" s="31"/>
+      <x:c r="O32"/>
     </x:row>
     <x:row r="33" ht="36" customHeight="1">
       <x:c r="A33" s="30"/>
@@ -1218,7 +1215,7 @@
       <x:c r="L33" s="31"/>
       <x:c r="M33" s="31"/>
       <x:c r="N33" s="38"/>
-      <x:c r="O33" s="31"/>
+      <x:c r="O33"/>
     </x:row>
     <x:row r="34" ht="36" customHeight="1">
       <x:c r="A34" s="30"/>
@@ -1235,7 +1232,7 @@
       <x:c r="L34" s="31"/>
       <x:c r="M34" s="31"/>
       <x:c r="N34" s="38"/>
-      <x:c r="O34" s="31"/>
+      <x:c r="O34"/>
     </x:row>
     <x:row r="35" ht="36" customHeight="1">
       <x:c r="A35" s="30"/>
@@ -1252,7 +1249,7 @@
       <x:c r="L35" s="31"/>
       <x:c r="M35" s="31"/>
       <x:c r="N35" s="38"/>
-      <x:c r="O35" s="31"/>
+      <x:c r="O35"/>
     </x:row>
     <x:row r="36" ht="36" customHeight="1">
       <x:c r="A36" s="30"/>
@@ -1269,7 +1266,7 @@
       <x:c r="L36" s="31"/>
       <x:c r="M36" s="31"/>
       <x:c r="N36" s="38"/>
-      <x:c r="O36" s="31"/>
+      <x:c r="O36"/>
     </x:row>
     <x:row r="37" ht="36" customHeight="1">
       <x:c r="A37" s="30"/>
@@ -1286,7 +1283,7 @@
       <x:c r="L37" s="31"/>
       <x:c r="M37" s="31"/>
       <x:c r="N37" s="38"/>
-      <x:c r="O37" s="31"/>
+      <x:c r="O37"/>
     </x:row>
     <x:row r="38" ht="36" customHeight="1">
       <x:c r="A38" s="30"/>
@@ -1303,7 +1300,7 @@
       <x:c r="L38" s="31"/>
       <x:c r="M38" s="31"/>
       <x:c r="N38" s="38"/>
-      <x:c r="O38" s="31"/>
+      <x:c r="O38"/>
     </x:row>
     <x:row r="39" ht="36" customHeight="1">
       <x:c r="A39" s="30"/>
@@ -1320,7 +1317,7 @@
       <x:c r="L39" s="31"/>
       <x:c r="M39" s="31"/>
       <x:c r="N39" s="38"/>
-      <x:c r="O39" s="31"/>
+      <x:c r="O39"/>
     </x:row>
     <x:row r="40" ht="36" customHeight="1">
       <x:c r="A40" s="30"/>
@@ -1337,7 +1334,7 @@
       <x:c r="L40" s="31"/>
       <x:c r="M40" s="31"/>
       <x:c r="N40" s="38"/>
-      <x:c r="O40" s="31"/>
+      <x:c r="O40"/>
     </x:row>
     <x:row r="41" ht="36" customHeight="1">
       <x:c r="A41" s="30"/>
@@ -1354,7 +1351,7 @@
       <x:c r="L41" s="31"/>
       <x:c r="M41" s="31"/>
       <x:c r="N41" s="38"/>
-      <x:c r="O41" s="31"/>
+      <x:c r="O41"/>
     </x:row>
     <x:row r="42" ht="36" customHeight="1">
       <x:c r="A42" s="30"/>
@@ -1371,7 +1368,7 @@
       <x:c r="L42" s="31"/>
       <x:c r="M42" s="31"/>
       <x:c r="N42" s="38"/>
-      <x:c r="O42" s="31"/>
+      <x:c r="O42"/>
     </x:row>
     <x:row r="43" ht="36" customHeight="1">
       <x:c r="A43" s="30"/>
@@ -1388,7 +1385,7 @@
       <x:c r="L43" s="31"/>
       <x:c r="M43" s="31"/>
       <x:c r="N43" s="38"/>
-      <x:c r="O43" s="31"/>
+      <x:c r="O43"/>
     </x:row>
     <x:row r="44" ht="36" customHeight="1">
       <x:c r="A44" s="30"/>
@@ -1405,7 +1402,7 @@
       <x:c r="L44" s="31"/>
       <x:c r="M44" s="31"/>
       <x:c r="N44" s="38"/>
-      <x:c r="O44" s="31"/>
+      <x:c r="O44"/>
     </x:row>
     <x:row r="45" ht="36" customHeight="1">
       <x:c r="A45" s="30"/>
@@ -1422,7 +1419,7 @@
       <x:c r="L45" s="31"/>
       <x:c r="M45" s="31"/>
       <x:c r="N45" s="38"/>
-      <x:c r="O45" s="31"/>
+      <x:c r="O45"/>
     </x:row>
     <x:row r="46" ht="36" customHeight="1">
       <x:c r="A46" s="30"/>
@@ -1439,7 +1436,7 @@
       <x:c r="L46" s="31"/>
       <x:c r="M46" s="31"/>
       <x:c r="N46" s="38"/>
-      <x:c r="O46" s="31"/>
+      <x:c r="O46"/>
     </x:row>
     <x:row r="47" ht="36" customHeight="1">
       <x:c r="A47" s="30"/>
@@ -1456,7 +1453,7 @@
       <x:c r="L47" s="31"/>
       <x:c r="M47" s="31"/>
       <x:c r="N47" s="38"/>
-      <x:c r="O47" s="31"/>
+      <x:c r="O47"/>
     </x:row>
     <x:row r="48" ht="36" customHeight="1">
       <x:c r="A48" s="30"/>
@@ -1473,7 +1470,7 @@
       <x:c r="L48" s="31"/>
       <x:c r="M48" s="31"/>
       <x:c r="N48" s="38"/>
-      <x:c r="O48" s="31"/>
+      <x:c r="O48"/>
     </x:row>
     <x:row r="49" ht="36" customHeight="1">
       <x:c r="A49" s="30"/>
@@ -1490,7 +1487,7 @@
       <x:c r="L49" s="31"/>
       <x:c r="M49" s="31"/>
       <x:c r="N49" s="38"/>
-      <x:c r="O49" s="31"/>
+      <x:c r="O49"/>
     </x:row>
     <x:row r="50" ht="36" customHeight="1">
       <x:c r="A50" s="30"/>
@@ -1507,7 +1504,7 @@
       <x:c r="L50" s="31"/>
       <x:c r="M50" s="31"/>
       <x:c r="N50" s="38"/>
-      <x:c r="O50" s="31"/>
+      <x:c r="O50"/>
     </x:row>
     <x:row r="51" ht="36" customHeight="1">
       <x:c r="A51" s="30"/>
@@ -1524,7 +1521,7 @@
       <x:c r="L51" s="31"/>
       <x:c r="M51" s="31"/>
       <x:c r="N51" s="38"/>
-      <x:c r="O51" s="31"/>
+      <x:c r="O51"/>
     </x:row>
     <x:row r="52" ht="36" customHeight="1">
       <x:c r="A52" s="30"/>
@@ -1541,7 +1538,7 @@
       <x:c r="L52" s="31"/>
       <x:c r="M52" s="31"/>
       <x:c r="N52" s="38"/>
-      <x:c r="O52" s="31"/>
+      <x:c r="O52"/>
     </x:row>
     <x:row r="53" ht="36" customHeight="1">
       <x:c r="A53" s="30"/>
@@ -1558,7 +1555,7 @@
       <x:c r="L53" s="31"/>
       <x:c r="M53" s="31"/>
       <x:c r="N53" s="38"/>
-      <x:c r="O53" s="31"/>
+      <x:c r="O53"/>
     </x:row>
     <x:row r="54" ht="36" customHeight="1">
       <x:c r="A54" s="30"/>
@@ -1575,7 +1572,7 @@
       <x:c r="L54" s="31"/>
       <x:c r="M54" s="31"/>
       <x:c r="N54" s="38"/>
-      <x:c r="O54" s="31"/>
+      <x:c r="O54"/>
     </x:row>
     <x:row r="55" ht="36" customHeight="1">
       <x:c r="A55" s="30"/>
@@ -1592,7 +1589,7 @@
       <x:c r="L55" s="31"/>
       <x:c r="M55" s="31"/>
       <x:c r="N55" s="38"/>
-      <x:c r="O55" s="31"/>
+      <x:c r="O55"/>
     </x:row>
     <x:row r="56" ht="36" customHeight="1">
       <x:c r="A56" s="30"/>
@@ -1609,7 +1606,7 @@
       <x:c r="L56" s="31"/>
       <x:c r="M56" s="31"/>
       <x:c r="N56" s="38"/>
-      <x:c r="O56" s="31"/>
+      <x:c r="O56"/>
     </x:row>
     <x:row r="57" ht="36" customHeight="1">
       <x:c r="A57" s="30"/>
@@ -1626,7 +1623,7 @@
       <x:c r="L57" s="31"/>
       <x:c r="M57" s="31"/>
       <x:c r="N57" s="38"/>
-      <x:c r="O57" s="31"/>
+      <x:c r="O57"/>
     </x:row>
     <x:row r="58" ht="36" customHeight="1">
       <x:c r="A58" s="30"/>
@@ -1643,7 +1640,7 @@
       <x:c r="L58" s="31"/>
       <x:c r="M58" s="31"/>
       <x:c r="N58" s="38"/>
-      <x:c r="O58" s="31"/>
+      <x:c r="O58"/>
     </x:row>
     <x:row r="59" ht="36" customHeight="1">
       <x:c r="A59" s="30"/>
@@ -1660,7 +1657,7 @@
       <x:c r="L59" s="31"/>
       <x:c r="M59" s="31"/>
       <x:c r="N59" s="38"/>
-      <x:c r="O59" s="31"/>
+      <x:c r="O59"/>
     </x:row>
     <x:row r="60" ht="36" customHeight="1">
       <x:c r="A60" s="30"/>
@@ -1677,7 +1674,7 @@
       <x:c r="L60" s="31"/>
       <x:c r="M60" s="31"/>
       <x:c r="N60" s="38"/>
-      <x:c r="O60" s="31"/>
+      <x:c r="O60"/>
     </x:row>
     <x:row r="61" ht="36" customHeight="1">
       <x:c r="A61" s="30"/>
@@ -1694,7 +1691,7 @@
       <x:c r="L61" s="31"/>
       <x:c r="M61" s="31"/>
       <x:c r="N61" s="38"/>
-      <x:c r="O61" s="31"/>
+      <x:c r="O61"/>
     </x:row>
     <x:row r="62" ht="36" customHeight="1">
       <x:c r="A62" s="30"/>
@@ -1711,7 +1708,7 @@
       <x:c r="L62" s="31"/>
       <x:c r="M62" s="31"/>
       <x:c r="N62" s="38"/>
-      <x:c r="O62" s="31"/>
+      <x:c r="O62"/>
     </x:row>
     <x:row r="63" ht="36" customHeight="1">
       <x:c r="A63" s="30"/>
@@ -1728,7 +1725,7 @@
       <x:c r="L63" s="31"/>
       <x:c r="M63" s="31"/>
       <x:c r="N63" s="38"/>
-      <x:c r="O63" s="31"/>
+      <x:c r="O63"/>
     </x:row>
     <x:row r="64" ht="36" customHeight="1">
       <x:c r="A64" s="30"/>
@@ -1745,7 +1742,7 @@
       <x:c r="L64" s="31"/>
       <x:c r="M64" s="31"/>
       <x:c r="N64" s="38"/>
-      <x:c r="O64" s="31"/>
+      <x:c r="O64"/>
     </x:row>
     <x:row r="65" ht="36" customHeight="1">
       <x:c r="A65" s="30"/>
@@ -1762,7 +1759,7 @@
       <x:c r="L65" s="31"/>
       <x:c r="M65" s="31"/>
       <x:c r="N65" s="38"/>
-      <x:c r="O65" s="31"/>
+      <x:c r="O65"/>
     </x:row>
     <x:row r="66" ht="36" customHeight="1">
       <x:c r="A66" s="30"/>
@@ -1779,7 +1776,7 @@
       <x:c r="L66" s="31"/>
       <x:c r="M66" s="31"/>
       <x:c r="N66" s="38"/>
-      <x:c r="O66" s="31"/>
+      <x:c r="O66"/>
     </x:row>
     <x:row r="67" ht="36" customHeight="1">
       <x:c r="A67" s="30"/>
@@ -1796,7 +1793,7 @@
       <x:c r="L67" s="31"/>
       <x:c r="M67" s="31"/>
       <x:c r="N67" s="38"/>
-      <x:c r="O67" s="31"/>
+      <x:c r="O67"/>
     </x:row>
     <x:row r="68" ht="36" customHeight="1">
       <x:c r="A68" s="30"/>
@@ -1813,7 +1810,7 @@
       <x:c r="L68" s="31"/>
       <x:c r="M68" s="31"/>
       <x:c r="N68" s="38"/>
-      <x:c r="O68" s="31"/>
+      <x:c r="O68"/>
     </x:row>
     <x:row r="69" ht="36" customHeight="1">
       <x:c r="A69" s="30"/>
@@ -1830,7 +1827,7 @@
       <x:c r="L69" s="31"/>
       <x:c r="M69" s="31"/>
       <x:c r="N69" s="38"/>
-      <x:c r="O69" s="31"/>
+      <x:c r="O69"/>
     </x:row>
     <x:row r="70" ht="36" customHeight="1">
       <x:c r="A70" s="30"/>
@@ -1847,7 +1844,7 @@
       <x:c r="L70" s="31"/>
       <x:c r="M70" s="31"/>
       <x:c r="N70" s="38"/>
-      <x:c r="O70" s="31"/>
+      <x:c r="O70"/>
     </x:row>
     <x:row r="71" ht="36" customHeight="1">
       <x:c r="A71" s="30"/>
@@ -1864,7 +1861,7 @@
       <x:c r="L71" s="31"/>
       <x:c r="M71" s="31"/>
       <x:c r="N71" s="38"/>
-      <x:c r="O71" s="31"/>
+      <x:c r="O71"/>
     </x:row>
     <x:row r="72" ht="36" customHeight="1">
       <x:c r="A72" s="30"/>
@@ -1881,7 +1878,7 @@
       <x:c r="L72" s="31"/>
       <x:c r="M72" s="31"/>
       <x:c r="N72" s="38"/>
-      <x:c r="O72" s="31"/>
+      <x:c r="O72"/>
     </x:row>
     <x:row r="73" ht="36" customHeight="1">
       <x:c r="A73" s="30"/>
@@ -1898,7 +1895,7 @@
       <x:c r="L73" s="31"/>
       <x:c r="M73" s="31"/>
       <x:c r="N73" s="38"/>
-      <x:c r="O73" s="31"/>
+      <x:c r="O73"/>
     </x:row>
     <x:row r="74" ht="36" customHeight="1">
       <x:c r="A74" s="30"/>
@@ -1915,7 +1912,7 @@
       <x:c r="L74" s="31"/>
       <x:c r="M74" s="31"/>
       <x:c r="N74" s="38"/>
-      <x:c r="O74" s="31"/>
+      <x:c r="O74"/>
     </x:row>
     <x:row r="75" ht="36" customHeight="1">
       <x:c r="A75" s="30"/>
@@ -1932,7 +1929,7 @@
       <x:c r="L75" s="31"/>
       <x:c r="M75" s="31"/>
       <x:c r="N75" s="38"/>
-      <x:c r="O75" s="31"/>
+      <x:c r="O75"/>
     </x:row>
     <x:row r="76" ht="36" customHeight="1">
       <x:c r="A76" s="30"/>
@@ -1949,7 +1946,7 @@
       <x:c r="L76" s="31"/>
       <x:c r="M76" s="31"/>
       <x:c r="N76" s="38"/>
-      <x:c r="O76" s="31"/>
+      <x:c r="O76"/>
     </x:row>
     <x:row r="77" ht="36" customHeight="1">
       <x:c r="A77" s="30"/>
@@ -1966,7 +1963,7 @@
       <x:c r="L77" s="31"/>
       <x:c r="M77" s="31"/>
       <x:c r="N77" s="38"/>
-      <x:c r="O77" s="31"/>
+      <x:c r="O77"/>
     </x:row>
     <x:row r="78" ht="36" customHeight="1">
       <x:c r="A78" s="30"/>
@@ -1983,7 +1980,7 @@
       <x:c r="L78" s="31"/>
       <x:c r="M78" s="31"/>
       <x:c r="N78" s="38"/>
-      <x:c r="O78" s="31"/>
+      <x:c r="O78"/>
     </x:row>
     <x:row r="79" ht="36" customHeight="1">
       <x:c r="A79" s="30"/>
@@ -2000,7 +1997,7 @@
       <x:c r="L79" s="31"/>
       <x:c r="M79" s="31"/>
       <x:c r="N79" s="38"/>
-      <x:c r="O79" s="31"/>
+      <x:c r="O79"/>
     </x:row>
     <x:row r="80" ht="36" customHeight="1">
       <x:c r="A80" s="30"/>
@@ -2017,7 +2014,7 @@
       <x:c r="L80" s="31"/>
       <x:c r="M80" s="31"/>
       <x:c r="N80" s="38"/>
-      <x:c r="O80" s="31"/>
+      <x:c r="O80"/>
     </x:row>
     <x:row r="81" ht="36" customHeight="1">
       <x:c r="A81" s="30"/>
@@ -2034,7 +2031,7 @@
       <x:c r="L81" s="31"/>
       <x:c r="M81" s="31"/>
       <x:c r="N81" s="38"/>
-      <x:c r="O81" s="31"/>
+      <x:c r="O81"/>
     </x:row>
     <x:row r="82" ht="36" customHeight="1">
       <x:c r="A82" s="30"/>
@@ -2051,7 +2048,7 @@
       <x:c r="L82" s="31"/>
       <x:c r="M82" s="31"/>
       <x:c r="N82" s="38"/>
-      <x:c r="O82" s="31"/>
+      <x:c r="O82"/>
     </x:row>
     <x:row r="83" ht="36" customHeight="1">
       <x:c r="A83" s="30"/>
@@ -2068,7 +2065,7 @@
       <x:c r="L83" s="31"/>
       <x:c r="M83" s="31"/>
       <x:c r="N83" s="38"/>
-      <x:c r="O83" s="31"/>
+      <x:c r="O83"/>
     </x:row>
     <x:row r="84" ht="36" customHeight="1">
       <x:c r="A84" s="30"/>
@@ -2085,7 +2082,7 @@
       <x:c r="L84" s="31"/>
       <x:c r="M84" s="31"/>
       <x:c r="N84" s="38"/>
-      <x:c r="O84" s="31"/>
+      <x:c r="O84"/>
     </x:row>
     <x:row r="85" ht="36" customHeight="1">
       <x:c r="A85" s="30"/>
@@ -2102,7 +2099,7 @@
       <x:c r="L85" s="31"/>
       <x:c r="M85" s="31"/>
       <x:c r="N85" s="38"/>
-      <x:c r="O85" s="31"/>
+      <x:c r="O85"/>
     </x:row>
     <x:row r="86" ht="36" customHeight="1">
       <x:c r="A86" s="30"/>
@@ -2119,7 +2116,7 @@
       <x:c r="L86" s="31"/>
       <x:c r="M86" s="31"/>
       <x:c r="N86" s="38"/>
-      <x:c r="O86" s="31"/>
+      <x:c r="O86"/>
     </x:row>
     <x:row r="87" ht="36" customHeight="1">
       <x:c r="A87" s="30"/>
@@ -2136,7 +2133,7 @@
       <x:c r="L87" s="31"/>
       <x:c r="M87" s="31"/>
       <x:c r="N87" s="38"/>
-      <x:c r="O87" s="31"/>
+      <x:c r="O87"/>
     </x:row>
     <x:row r="88" ht="36" customHeight="1">
       <x:c r="A88" s="30"/>
@@ -2153,7 +2150,7 @@
       <x:c r="L88" s="31"/>
       <x:c r="M88" s="31"/>
       <x:c r="N88" s="38"/>
-      <x:c r="O88" s="31"/>
+      <x:c r="O88"/>
     </x:row>
     <x:row r="89" ht="36" customHeight="1">
       <x:c r="A89" s="30"/>
@@ -2170,7 +2167,7 @@
       <x:c r="L89" s="31"/>
       <x:c r="M89" s="31"/>
       <x:c r="N89" s="38"/>
-      <x:c r="O89" s="31"/>
+      <x:c r="O89"/>
     </x:row>
     <x:row r="90" ht="36" customHeight="1">
       <x:c r="A90" s="30"/>
@@ -2187,7 +2184,7 @@
       <x:c r="L90" s="31"/>
       <x:c r="M90" s="31"/>
       <x:c r="N90" s="38"/>
-      <x:c r="O90" s="31"/>
+      <x:c r="O90"/>
     </x:row>
     <x:row r="91" ht="36" customHeight="1">
       <x:c r="A91" s="30"/>
@@ -2204,7 +2201,7 @@
       <x:c r="L91" s="31"/>
       <x:c r="M91" s="31"/>
       <x:c r="N91" s="38"/>
-      <x:c r="O91" s="31"/>
+      <x:c r="O91"/>
     </x:row>
     <x:row r="92" ht="36" customHeight="1">
       <x:c r="A92" s="30"/>
@@ -2221,7 +2218,7 @@
       <x:c r="L92" s="31"/>
       <x:c r="M92" s="31"/>
       <x:c r="N92" s="38"/>
-      <x:c r="O92" s="31"/>
+      <x:c r="O92"/>
     </x:row>
     <x:row r="93" ht="36" customHeight="1">
       <x:c r="A93" s="30"/>
@@ -2238,7 +2235,7 @@
       <x:c r="L93" s="31"/>
       <x:c r="M93" s="31"/>
       <x:c r="N93" s="38"/>
-      <x:c r="O93" s="31"/>
+      <x:c r="O93"/>
     </x:row>
     <x:row r="94" ht="36" customHeight="1">
       <x:c r="A94" s="30"/>
@@ -2255,7 +2252,7 @@
       <x:c r="L94" s="31"/>
       <x:c r="M94" s="31"/>
       <x:c r="N94" s="38"/>
-      <x:c r="O94" s="31"/>
+      <x:c r="O94"/>
     </x:row>
     <x:row r="95" ht="36" customHeight="1">
       <x:c r="A95" s="30"/>
@@ -2272,7 +2269,7 @@
       <x:c r="L95" s="31"/>
       <x:c r="M95" s="31"/>
       <x:c r="N95" s="38"/>
-      <x:c r="O95" s="31"/>
+      <x:c r="O95"/>
     </x:row>
     <x:row r="96" ht="36" customHeight="1">
       <x:c r="A96" s="30"/>
@@ -2289,7 +2286,7 @@
       <x:c r="L96" s="31"/>
       <x:c r="M96" s="31"/>
       <x:c r="N96" s="38"/>
-      <x:c r="O96" s="31"/>
+      <x:c r="O96"/>
     </x:row>
     <x:row r="97" ht="36" customHeight="1">
       <x:c r="A97" s="30"/>
@@ -2306,7 +2303,7 @@
       <x:c r="L97" s="31"/>
       <x:c r="M97" s="31"/>
       <x:c r="N97" s="38"/>
-      <x:c r="O97" s="31"/>
+      <x:c r="O97"/>
     </x:row>
     <x:row r="98" ht="36" customHeight="1">
       <x:c r="A98" s="30"/>
@@ -2323,7 +2320,7 @@
       <x:c r="L98" s="31"/>
       <x:c r="M98" s="31"/>
       <x:c r="N98" s="38"/>
-      <x:c r="O98" s="31"/>
+      <x:c r="O98"/>
     </x:row>
     <x:row r="99" ht="36" customHeight="1">
       <x:c r="A99" s="30"/>
@@ -2340,7 +2337,7 @@
       <x:c r="L99" s="31"/>
       <x:c r="M99" s="31"/>
       <x:c r="N99" s="38"/>
-      <x:c r="O99" s="31"/>
+      <x:c r="O99"/>
     </x:row>
     <x:row r="100" ht="36" customHeight="1">
       <x:c r="A100" s="30"/>
@@ -2357,7 +2354,7 @@
       <x:c r="L100" s="31"/>
       <x:c r="M100" s="31"/>
       <x:c r="N100" s="38"/>
-      <x:c r="O100" s="31"/>
+      <x:c r="O100"/>
     </x:row>
     <x:row r="101" ht="36" customHeight="1">
       <x:c r="A101" s="30"/>
@@ -2374,7 +2371,7 @@
       <x:c r="L101" s="31"/>
       <x:c r="M101" s="31"/>
       <x:c r="N101" s="38"/>
-      <x:c r="O101" s="31"/>
+      <x:c r="O101"/>
     </x:row>
     <x:row r="102" ht="36" customHeight="1">
       <x:c r="A102" s="30"/>
@@ -2391,7 +2388,7 @@
       <x:c r="L102" s="31"/>
       <x:c r="M102" s="31"/>
       <x:c r="N102" s="38"/>
-      <x:c r="O102" s="31"/>
+      <x:c r="O102"/>
     </x:row>
     <x:row r="103" ht="36" customHeight="1">
       <x:c r="A103" s="30"/>
@@ -2408,7 +2405,7 @@
       <x:c r="L103" s="31"/>
       <x:c r="M103" s="31"/>
       <x:c r="N103" s="38"/>
-      <x:c r="O103" s="31"/>
+      <x:c r="O103"/>
     </x:row>
     <x:row r="104" ht="36" customHeight="1">
       <x:c r="A104" s="30"/>
@@ -2425,7 +2422,7 @@
       <x:c r="L104" s="31"/>
       <x:c r="M104" s="31"/>
       <x:c r="N104" s="38"/>
-      <x:c r="O104" s="31"/>
+      <x:c r="O104"/>
     </x:row>
     <x:row r="105" ht="36" customHeight="1">
       <x:c r="A105" s="30"/>
@@ -2442,7 +2439,7 @@
       <x:c r="L105" s="31"/>
       <x:c r="M105" s="31"/>
       <x:c r="N105" s="38"/>
-      <x:c r="O105" s="31"/>
+      <x:c r="O105"/>
     </x:row>
     <x:row r="106" ht="36" customHeight="1">
       <x:c r="A106" s="30"/>
@@ -2459,7 +2456,7 @@
       <x:c r="L106" s="31"/>
       <x:c r="M106" s="31"/>
       <x:c r="N106" s="38"/>
-      <x:c r="O106" s="31"/>
+      <x:c r="O106"/>
     </x:row>
     <x:row r="107" ht="36" customHeight="1">
       <x:c r="A107" s="32"/>
@@ -2476,7 +2473,7 @@
       <x:c r="L107" s="33"/>
       <x:c r="M107" s="33"/>
       <x:c r="N107" s="39"/>
-      <x:c r="O107" s="33"/>
+      <x:c r="O107"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A8:A107">
@@ -2510,7 +2507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1ce5ace60aa4f62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a7df74efede4f95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2618,12 +2615,12 @@
         <x:v>Leave blank to use the region’s default address below. Enter another starting address if this opportunity uses a different origin.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="40" customHeight="1">
+    <x:row r="14" ht="43" customHeight="1">
       <x:c r="A14" s="54" t="str">
-        <x:v>Contact details</x:v>
+        <x:v>Link</x:v>
       </x:c>
       <x:c r="B14" s="56" t="str">
-        <x:v>Enter the project contact’s name and email in their columns. Put phone numbers or other contact information in Notes.</x:v>
+        <x:v>Optional project or document URL. Paste the address or use Insert &gt; Link. HTTP and HTTPS are supported. Do not use a HYPERLINK formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="40" customHeight="1">
